--- a/healthcare_assessment_forms/034_respiratory_therapist_skills_checklist--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/034_respiratory_therapist_skills_checklist--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -751,29 +751,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>certified_pulmonary_rehabilitation_specialist</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Certified Pulmonary Rehabilitation Specialist</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>licensure_choices</t>
+          <t>core_skills_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>cardiac_pulmonary_rehabilitation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Cardiac Pulmonary Rehabilitation</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cardiac_pulmonary_rehabilitation</t>
+          <t>pulmonary_rehabilitation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cardiac Pulmonary Rehabilitation</t>
+          <t>Pulmonary Rehabilitation</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pulmonary_rehabilitation</t>
+          <t>cardiopulmonary_resuscitation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pulmonary Rehabilitation</t>
+          <t>Cardiopulmonary Resuscitation</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cardiopulmonary_resuscitation</t>
+          <t>ventilatory_care</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cardiopulmonary Resuscitation</t>
+          <t>Ventilatory Care</t>
         </is>
       </c>
     </row>
@@ -836,29 +836,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ventilatory_care</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ventilatory Care</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>core_skills_choices</t>
+          <t>equipment_proficiency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>incentive_spirometer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Incentive Spirometer</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>incentive_spirometer</t>
+          <t>pft_spirometer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Incentive Spirometer</t>
+          <t>PFT Spirometer</t>
         </is>
       </c>
     </row>
@@ -887,29 +887,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pft_spirometer</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PFT Spirometer</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equipment_proficiency_choices</t>
+          <t>hiring_staffing_training_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>new_hire</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>New Hire</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>new_hire</t>
+          <t>staffing_decision</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New Hire</t>
+          <t>Staffing Decision</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>staffing_decision</t>
+          <t>training_decision</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Staffing Decision</t>
+          <t>Training Decision</t>
         </is>
       </c>
     </row>
@@ -955,27 +955,10 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>training_decision</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
-        <is>
-          <t>Training Decision</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>hiring_staffing_training_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Other (please specify)</t>
         </is>
